--- a/results/final_0624_summary/CHD_49_BinaryVector_summary.xlsx
+++ b/results/final_0624_summary/CHD_49_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,80 +456,260 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>example_precision__0.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>f1__0.0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1__0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f1__0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1__0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.3</t>
         </is>
@@ -563,80 +743,260 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.6434±0.0195</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.6206±0.0255</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5880±0.0309</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5229±0.0300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.7468±0.0244</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.7438±0.0331</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.7607±0.0271</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.7754±0.0451</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.6658±0.0157</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.6514±0.0215</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.6349±0.0269</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.5949±0.0285</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.7051±0.0119</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.6863±0.0157</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.6520±0.0257</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.5832±0.0232</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5600±0.0182</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5421±0.0224</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5147±0.0286</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.4631±0.0280</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.5305±0.0101</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5201±0.0181</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5237±0.0273</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5209±0.0280</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4975±0.0051</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4819±0.0167</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.4620±0.0286</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.4415±0.0267</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5885±0.0198</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5889±0.0273</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6210±0.0281</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.6894±0.0695</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.9981±0.0037</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.9837±0.0143</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.9731±0.0216</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.8423±0.0465</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6898±0.0155</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.6767±0.0190</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.6573±0.0282</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.6190±0.0257</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.6294±0.0170</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6076±0.0222</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.5703±0.0351</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.5100±0.0255</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7637±0.0250</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.7647±0.0290</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.7771±0.0265</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7888±0.0414</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.2000±0.0209</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.1703±0.0278</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.1063±0.0341</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.0505±0.0214</t>
         </is>
@@ -670,80 +1030,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.6403±0.0223</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6161±0.0262</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.5856±0.0288</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.5223±0.0276</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.7699±0.0275</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.7606±0.0365</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.7768±0.0247</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.7849±0.0427</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.6727±0.0191</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.6547±0.0233</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.6390±0.0252</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.5983±0.0266</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.7057±0.0119</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6841±0.0181</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6512±0.0245</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0.5838±0.0217</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5644±0.0229</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.5432±0.0242</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.5176±0.0253</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.4661±0.0251</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.5385±0.0122</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.5255±0.0190</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.5292±0.0250</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.5243±0.0263</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.4967±0.0087</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.4789±0.0172</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.4621±0.0259</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.4425±0.0244</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6076±0.0213</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6035±0.0286</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6351±0.0254</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6983±0.0678</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.9981±0.0037</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.9874±0.0125</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>0.9755±0.0208</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.8522±0.0503</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6955±0.0184</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0209</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6609±0.0266</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6220±0.0237</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6260±0.0202</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6026±0.0236</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.5682±0.0336</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.5103±0.0234</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7830±0.0278</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7798±0.0313</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7911±0.0222</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7980±0.0387</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.1928±0.0265</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.1622±0.0231</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.1036±0.0297</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.0495±0.0194</t>
         </is>
@@ -777,80 +1317,260 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.6433±0.0188</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.6210±0.0257</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.5868±0.0320</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.5214±0.0287</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.7472±0.0241</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.7449±0.0332</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.7579±0.0272</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.7747±0.0446</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.6660±0.0146</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.6520±0.0217</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.6331±0.0277</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.5940±0.0280</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.7051±0.0115</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.6872±0.0159</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.6506±0.0264</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.5821±0.0230</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5604±0.0171</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5425±0.0226</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.5130±0.0293</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.4619±0.0274</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.5307±0.0098</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.5214±0.0188</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.5228±0.0273</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.5201±0.0279</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.4974±0.0032</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.4833±0.0172</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.4618±0.0290</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.4409±0.0263</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5889±0.0202</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5896±0.0276</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.6189±0.0278</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.6883±0.0692</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.9963±0.0046</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.9837±0.0143</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>0.9719±0.0217</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>0.8423±0.0449</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.6898±0.0147</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.6775±0.0190</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.6556±0.0289</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.6181±0.0254</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.6294±0.0164</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.6085±0.0217</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5693±0.0359</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5092±0.0247</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.7638±0.0247</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.7651±0.0290</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.7743±0.0265</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.7878±0.0412</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.2036±0.0246</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.1694±0.0264</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>0.1063±0.0355</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.0486±0.0177</t>
         </is>
@@ -884,80 +1604,260 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.6400±0.0214</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.6159±0.0271</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.5852±0.0289</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.5213±0.0273</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.7704±0.0270</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.7606±0.0376</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.7773±0.0244</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.7851±0.0416</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.6727±0.0179</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.6546±0.0247</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.6388±0.0252</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.5980±0.0260</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.7054±0.0113</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.6842±0.0189</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.6508±0.0242</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.5833±0.0214</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5644±0.0216</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.5431±0.0257</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.5173±0.0248</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.4658±0.0247</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.5384±0.0116</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.5256±0.0208</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.5297±0.0239</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.5243±0.0262</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.4968±0.0071</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.4791±0.0181</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.4625±0.0253</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.4424±0.0245</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.6077±0.0212</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.6036±0.0297</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.6359±0.0238</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.6984±0.0674</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.9981±0.0037</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.9874±0.0125</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>0.9744±0.0210</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.8534±0.0495</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.6953±0.0173</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.6795±0.0221</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.6606±0.0264</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.6219±0.0233</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.6257±0.0193</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.6027±0.0240</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.5678±0.0337</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.5100±0.0233</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.7831±0.0272</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.7798±0.0322</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.7910±0.0214</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.7983±0.0377</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.1928±0.0265</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.1622±0.0231</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>0.1018±0.0291</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.0495±0.0194</t>
         </is>
@@ -991,80 +1891,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.6851±0.0405</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.6629±0.0281</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.6625±0.0277</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.5948±0.0401</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.6577±0.0341</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.6236±0.0352</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.5880±0.0273</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.5557±0.0232</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.6451±0.0308</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.6172±0.0255</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.5962±0.0223</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.5459±0.0288</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.7177±0.0251</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.6973±0.0179</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.6880±0.0185</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.6387±0.0192</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.5354±0.0333</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5055±0.0242</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.4819±0.0227</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.4263±0.0255</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.4861±0.0260</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.4637±0.0242</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.4479±0.0222</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.4377±0.0294</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.5267±0.0242</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.5061±0.0166</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.5000±0.0246</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.4587±0.0352</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.4856±0.0231</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4605±0.0261</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.4373±0.0244</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.4307±0.0273</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.9898±0.0096</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.9800±0.0147</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>0.9023±0.0954</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.6664±0.0303</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.6396±0.0222</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.6211±0.0247</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.5704±0.0257</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.6780±0.0393</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.6551±0.0235</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.6498±0.0283</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.5841±0.0375</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.6564±0.0335</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.6256±0.0307</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.5958±0.0318</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.5582±0.0207</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.1784±0.0270</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.1514±0.0290</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>0.1270±0.0243</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.0766±0.0210</t>
         </is>
@@ -1098,80 +2178,260 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.6469±0.0232</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.6240±0.0294</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.6060±0.0312</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.5572±0.0404</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.7657±0.0265</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.7584±0.0358</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.7616±0.0208</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.7420±0.0405</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.6751±0.0180</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.6575±0.0237</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.6467±0.0203</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.6073±0.0338</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.7117±0.0102</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.6913±0.0167</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.6748±0.0167</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.6272±0.0269</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.5671±0.0220</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.5444±0.0243</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.5277±0.0203</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.4787±0.0316</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.5420±0.0087</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.5270±0.0169</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.5281±0.0157</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.5159±0.0345</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.5016±0.0097</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.4804±0.0162</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.4739±0.0222</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.4530±0.0326</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.6028±0.0186</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.5960±0.0300</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.6086±0.0235</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.6255±0.0690</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.9981±0.0037</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.9886±0.0109</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>0.9755±0.0112</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.8831±0.0510</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.6978±0.0166</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.6813±0.0212</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.6710±0.0174</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.6336±0.0272</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.6349±0.0220</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.6127±0.0267</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.5945±0.0305</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.5493±0.0334</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.7755±0.0260</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.7688±0.0344</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.7720±0.0186</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.7504±0.0295</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.1910±0.0454</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>0.1649±0.0202</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>0.1216±0.0345</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.0631±0.0228</t>
         </is>
@@ -1205,80 +2465,260 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0.6836±0.0432</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.6646±0.0276</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.6691±0.0293</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.5968±0.0400</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.6090±0.0350</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.5854±0.0377</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.5569±0.0294</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.5291±0.0249</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.6193±0.0353</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.5949±0.0268</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.5797±0.0237</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.5320±0.0284</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.7051±0.0246</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.6887±0.0211</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.6827±0.0178</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.6366±0.0182</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.5063±0.0374</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.4812±0.0266</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.4627±0.0232</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.4142±0.0244</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.4525±0.0328</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.4416±0.0280</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.4313±0.0190</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.4307±0.0309</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.5189±0.0325</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.5040±0.0195</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.4985±0.0232</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.4612±0.0368</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.4430±0.0223</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4258±0.0289</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.4087±0.0180</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.4158±0.0306</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.9889±0.0107</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.9730±0.0183</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>0.8760±0.1251</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.6378±0.0334</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.6162±0.0258</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.6024±0.0249</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.5581±0.0255</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.6755±0.0420</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.6556±0.0242</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.6528±0.0290</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.5852±0.0376</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.6049±0.0327</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.5820±0.0344</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.5599±0.0293</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.5340±0.0204</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.1550±0.0319</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>0.1342±0.0272</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>0.1171±0.0217</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.0739±0.0192</t>
         </is>
@@ -1312,80 +2752,260 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.6481±0.0254</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.6232±0.0282</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.6057±0.0316</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.5548±0.0405</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.7666±0.0254</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.7595±0.0332</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.7612±0.0195</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.7413±0.0413</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.6762±0.0197</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.6573±0.0218</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.6461±0.0211</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.6055±0.0344</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.7132±0.0124</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.6907±0.0147</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.6740±0.0178</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.6251±0.0275</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.5684±0.0239</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.5439±0.0216</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.5264±0.0212</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.4769±0.0322</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.5439±0.0110</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.5272±0.0141</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.5279±0.0174</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.5139±0.0364</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.5044±0.0136</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.4801±0.0154</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.4749±0.0245</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.4507±0.0338</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.6038±0.0181</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.5965±0.0270</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.6073±0.0223</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.6242±0.0699</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.9958±0.0052</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.9886±0.0109</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>0.9758±0.0115</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>0.8831±0.0511</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.6991±0.0180</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.6810±0.0191</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.6701±0.0185</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.6321±0.0283</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.6366±0.0238</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.6120±0.0262</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.5939±0.0313</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.5473±0.0340</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.7761±0.0251</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.7691±0.0314</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.7706±0.0174</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.7496±0.0310</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.1928±0.0465</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>0.1658±0.0198</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>0.1189±0.0327</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.0649±0.0234</t>
         </is>
@@ -1419,80 +3039,260 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.6776±0.0226</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.6653±0.0276</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.6516±0.0306</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.5881±0.0455</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.6462±0.0313</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.6360±0.0346</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.6249±0.0334</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.5672±0.0264</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.6321±0.0170</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>0.6178±0.0232</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.6018±0.0276</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>0.5396±0.0309</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0.7117±0.0147</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.7021±0.0165</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.6874±0.0125</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.6411±0.0231</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.5222±0.0148</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.5051±0.0241</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.4854±0.0266</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.4226±0.0287</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.4766±0.0172</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.4709±0.0175</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.4663±0.0265</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.4455±0.0317</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.5177±0.0135</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.5040±0.0169</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.4821±0.0227</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.4556±0.0387</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.4794±0.0258</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.4741±0.0213</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.4706±0.0338</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.4449±0.0329</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>0.9991±0.0028</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>0.9917±0.0126</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>0.9261±0.0962</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.6616±0.0174</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.6508±0.0234</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.6345±0.0234</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.5809±0.0262</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.6680±0.0203</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.6559±0.0282</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.6374±0.0266</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.5852±0.0451</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.6566±0.0314</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.6467±0.0307</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.6328±0.0338</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.5784±0.0211</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.1640±0.0175</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>0.1441±0.0285</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>0.1189±0.0209</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.0667±0.0229</t>
         </is>
@@ -1526,80 +3326,260 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>0.6622±0.0320</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.6608±0.0349</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.6388±0.0374</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.5841±0.0261</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.6929±0.0139</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.6669±0.0268</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.6212±0.0174</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.5620±0.0398</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>0.6508±0.0163</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.6329±0.0231</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.5948±0.0203</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.5337±0.0269</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.7147±0.0140</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.7026±0.0202</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.6824±0.0198</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.6395±0.0170</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.5461±0.0183</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.5250±0.0264</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.4800±0.0218</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.4170±0.0254</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.5179±0.0085</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.4989±0.0217</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.4713±0.0133</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.4468±0.0277</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0.5135±0.0202</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.5014±0.0324</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.4836±0.0271</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.4612±0.0284</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.5374±0.0127</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.5126±0.0215</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.4752±0.0158</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.4454±0.0415</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.9991±0.0028</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>0.9944±0.0075</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.8843±0.1306</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.6794±0.0154</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.6615±0.0260</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.6305±0.0212</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.5749±0.0243</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.6581±0.0322</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.6481±0.0375</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.6322±0.0375</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.5832±0.0262</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.7036±0.0161</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.6769±0.0274</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.6304±0.0205</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.5684±0.0371</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.1946±0.0271</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0.1712±0.0360</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>0.1180±0.0253</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.0694±0.0261</t>
         </is>
@@ -1633,82 +3613,1123 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>0.7314±0.0369</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.6701±0.0351</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.6333±0.0401</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.4714±0.0598</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.4329±0.0098</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.3872±0.0178</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.3714±0.0197</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.2638±0.0411</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>0.5131±0.0178</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>0.4616±0.0188</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.4384±0.0208</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>0.3161±0.0444</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>0.6877±0.0129</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.6746±0.0093</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0.6644±0.0088</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.6261±0.0136</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.3966±0.0175</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.3545±0.0165</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.3375±0.0170</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.2379±0.0346</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.2872±0.0170</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.2891±0.0148</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.2865±0.0265</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.2376±0.0313</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.4386±0.0944</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.5308±0.0968</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.5144±0.0662</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.4774±0.0849</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.2762±0.0148</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.2547±0.0163</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.2465±0.0259</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.1791±0.0293</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>0.9991±0.0028</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>0.9944±0.0062</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.5465±0.0167</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.5091±0.0165</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.4891±0.0197</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.3745±0.0407</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.7280±0.0411</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>0.7269±0.0475</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.7102±0.0470</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.6688±0.0642</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.4377±0.0079</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0.3931±0.0201</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0.3745±0.0237</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.2620±0.0379</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
         <is>
           <t>0.0847±0.0271</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>0.0694±0.0239</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>0.0739±0.0270</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.0396±0.0202</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.5746±0.0341</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.6043±0.0327</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.5942±0.0433</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.4733±0.0699</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.6584±0.0361</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.6567±0.0277</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.6479±0.0284</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.6090±0.0354</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.7145±0.0371</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.6842±0.0326</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.6681±0.0343</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.6260±0.0463</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.6595±0.0299</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.6425±0.0242</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.6276±0.0204</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.5799±0.0394</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.7135±0.0189</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.7065±0.0166</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.6986±0.0132</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.6586±0.0186</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.5535±0.0311</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.5315±0.0247</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.5176±0.0197</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.4579±0.0374</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.5200±0.0218</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.4977±0.0153</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.4931±0.0228</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.4712±0.0257</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.5075±0.0194</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.5023±0.0178</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.4999±0.0185</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.4670±0.0222</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.5525±0.0229</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.5213±0.0190</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.5153±0.0337</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.4900±0.0347</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>0.9944±0.0075</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.9486±0.0531</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.6850±0.0252</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.6710±0.0217</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.6614±0.0193</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.6137±0.0338</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.6491±0.0277</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.6473±0.0257</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.6400±0.0267</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.5961±0.0292</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.7257±0.0300</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.6973±0.0281</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.6858±0.0331</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.6335±0.0481</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.1892±0.0317</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.1550±0.0348</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.1450±0.0211</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.0811±0.0221</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.5001±0.0359</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.4649±0.0443</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.4131±0.0681</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.2604±0.0699</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.6324±0.0262</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.6078±0.0258</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.5653±0.0275</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.5133±0.0407</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.6837±0.0204</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.6452±0.0348</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.5946±0.0258</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.5397±0.0491</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.6292±0.0141</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.5947±0.0246</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.5477±0.0191</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.4907±0.0427</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.6916±0.0070</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.6653±0.0183</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.6314±0.0151</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.5880±0.0252</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.5274±0.0164</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.4846±0.0257</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.4346±0.0189</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.3742±0.0368</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.5089±0.0099</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.4796±0.0212</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.4568±0.0301</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.4451±0.0390</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.4881±0.0175</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.4663±0.0249</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.4483±0.0308</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.4460±0.0350</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.5408±0.0158</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.5011±0.0278</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.4753±0.0405</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.4778±0.0745</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>0.9786±0.0139</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.8822±0.0998</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.6056±0.2225</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.6608±0.0110</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.6253±0.0237</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.5859±0.0198</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.5338±0.0381</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.6273±0.0261</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.6030±0.0265</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.5672±0.0280</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.5194±0.0393</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.6994±0.0163</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.6509±0.0361</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.6075±0.0318</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.5502±0.0452</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.2036±0.0405</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.1396±0.0302</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.0874±0.0180</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0432±0.0175</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.5876±0.0497</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.5773±0.0684</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.4844±0.0722</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.4235±0.0682</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.6379±0.0445</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.6299±0.0262</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.6000±0.0395</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.5573±0.0405</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.6165±0.0357</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.5976±0.0542</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.5649±0.0468</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.5434±0.0354</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.5965±0.0227</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.5765±0.0268</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.5451±0.0394</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.5131±0.0321</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.6769±0.0175</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.6674±0.0187</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0.6491±0.0235</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.6174±0.0252</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.4836±0.0227</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.4605±0.0256</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.4330±0.0375</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.3970±0.0299</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.4534±0.0185</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.4368±0.0299</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.4370±0.0255</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.4318±0.0258</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.4744±0.0275</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.4609±0.0281</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.4547±0.0272</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.4429±0.0306</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.4613±0.0238</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.4425±0.0426</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.4351±0.0366</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.4445±0.0341</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>0.9954±0.0139</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>0.9787±0.0278</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.8838±0.1257</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.6245±0.0206</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.6078±0.0266</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.5832±0.0333</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.5544±0.0266</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.6255±0.0390</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.6177±0.0321</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>0.5963±0.0378</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.5559±0.0301</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.6254±0.0227</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.6017±0.0510</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>0.5727±0.0437</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.5543±0.0351</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.1351±0.0242</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.1036±0.0239</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.0991±0.0285</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0631±0.0242</t>
         </is>
       </c>
     </row>
